--- a/outputs/Block2_National_Final_Selection_v12.xlsx
+++ b/outputs/Block2_National_Final_Selection_v12.xlsx
@@ -516,10 +516,10 @@
         <v>5.2778760639537</v>
       </c>
       <c r="F2">
-        <v>0.5680217180041788</v>
+        <v>0.5680217180041789</v>
       </c>
       <c r="G2">
-        <v>0.4319782819958211</v>
+        <v>0.4319782819958212</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>

--- a/outputs/Block2_National_Final_Selection_v12.xlsx
+++ b/outputs/Block2_National_Final_Selection_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Group</t>
   </si>
@@ -64,34 +64,16 @@
     <t>Popular Vote</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
     <t>ExpectedVoteAnchor</t>
   </si>
   <si>
-    <t>Ridge</t>
-  </si>
-  <si>
     <t>max_depth=3; max_features=0.5; min_samples_leaf=1</t>
   </si>
   <si>
-    <t>max_depth=None; max_features=sqrt; min_samples_leaf=1</t>
-  </si>
-  <si>
-    <t>alpha=1.0; solver=lsqr</t>
-  </si>
-  <si>
     <t>alpha=10.0; solver=lsqr</t>
   </si>
   <si>
     <t>D-R popular vote margin MAE (percentage points)</t>
-  </si>
-  <si>
-    <t>Mean target MAE in native units</t>
   </si>
 </sst>
 </file>
@@ -449,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -504,37 +486,37 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>8.020000000000001</v>
       </c>
       <c r="D2">
-        <v>3.214965175101933</v>
+        <v>4.279249385344345</v>
       </c>
       <c r="E2">
-        <v>5.2778760639537</v>
+        <v>4.766301551609027</v>
       </c>
       <c r="F2">
-        <v>0.5680217180041789</v>
+        <v>0.5687073277931841</v>
       </c>
       <c r="G2">
-        <v>0.4319782819958212</v>
+        <v>0.4312926722068158</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>0.02</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M2">
         <v>2.259284845582338</v>
@@ -544,82 +526,6 @@
       </c>
       <c r="O2">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>6.4</v>
-      </c>
-      <c r="D3">
-        <v>4.997511551750367</v>
-      </c>
-      <c r="E3">
-        <v>5.548289064960619</v>
-      </c>
-      <c r="F3">
-        <v>0.5173576334208475</v>
-      </c>
-      <c r="G3">
-        <v>0.4826423665791525</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3">
-        <v>0.02</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
-        <v>1.3375</v>
-      </c>
-      <c r="D4">
-        <v>1.005925204663541</v>
-      </c>
-      <c r="E4">
-        <v>1.091907339871432</v>
-      </c>
-      <c r="F4">
-        <v>0.5299749258901527</v>
-      </c>
-      <c r="G4">
-        <v>0.4700250741098472</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4">
-        <v>0.02</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_National_Final_Selection_v12.xlsx
+++ b/outputs/Block2_National_Final_Selection_v12.xlsx
@@ -495,13 +495,13 @@
         <v>4.279249385344345</v>
       </c>
       <c r="E2">
-        <v>4.766301551609027</v>
+        <v>4.766301551609024</v>
       </c>
       <c r="F2">
-        <v>0.5687073277931841</v>
+        <v>0.5687073277931843</v>
       </c>
       <c r="G2">
-        <v>0.4312926722068158</v>
+        <v>0.4312926722068157</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>

--- a/outputs/Block2_National_Final_Selection_v12.xlsx
+++ b/outputs/Block2_National_Final_Selection_v12.xlsx
@@ -495,13 +495,13 @@
         <v>4.279249385344345</v>
       </c>
       <c r="E2">
-        <v>4.766301551609024</v>
+        <v>4.766301551609027</v>
       </c>
       <c r="F2">
-        <v>0.5687073277931843</v>
+        <v>0.5687073277931841</v>
       </c>
       <c r="G2">
-        <v>0.4312926722068157</v>
+        <v>0.4312926722068158</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
